--- a/SQL+SUPABASE/BD_barbearia/modelo_tabelas.xlsx
+++ b/SQL+SUPABASE/BD_barbearia/modelo_tabelas.xlsx
@@ -4,19 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240" activeTab="1"/>
+    <workbookView xWindow="90" yWindow="135" windowWidth="22935" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
-    <sheet name="enderecos" sheetId="2" r:id="rId2"/>
-    <sheet name="Plan3" sheetId="3" r:id="rId3"/>
+    <sheet name="Plan3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -24,15 +23,6 @@
     <t>nome</t>
   </si>
   <si>
-    <t>logradouro</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>id_cliente</t>
-  </si>
-  <si>
     <t>Leandro</t>
   </si>
   <si>
@@ -42,21 +32,6 @@
     <t>Marize</t>
   </si>
   <si>
-    <t>Rua Eugênio Flor 790</t>
-  </si>
-  <si>
-    <t>Residencial</t>
-  </si>
-  <si>
-    <t>Rua Brasilio de Lara 66</t>
-  </si>
-  <si>
-    <t>Av Hugo Simas 1200</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
     <t>Guilherme</t>
   </si>
   <si>
@@ -66,26 +41,29 @@
     <t>status</t>
   </si>
   <si>
-    <t>(41) 99999-8888</t>
-  </si>
-  <si>
     <t>ativo</t>
   </si>
   <si>
-    <t>(41) 99999-7777</t>
-  </si>
-  <si>
-    <t>(41) 99999-6666</t>
-  </si>
-  <si>
-    <t>(41) 99999-5555</t>
+    <t>email</t>
+  </si>
+  <si>
+    <t>le21brad@gmail.com</t>
+  </si>
+  <si>
+    <t>lucas240613@gmail.com</t>
+  </si>
+  <si>
+    <t>marizefreitas01@gmail.com</t>
+  </si>
+  <si>
+    <t>guilherme@hotmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +78,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,10 +104,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -133,8 +122,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -427,14 +420,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,149 +436,99 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>41999998888</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>41999997777</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>41999996666</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
+      <c r="D5">
+        <v>41999995555</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="10.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
